--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,14 +880,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45163.60860790963</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -943,17 +939,6 @@
       <c r="F11" s="26" t="n"/>
       <c r="G11" s="26" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1009,7 +994,7 @@
       </c>
       <c r="C29" s="43" t="n"/>
       <c r="D29" s="44" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1025,10 +1010,9 @@
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>149.5</v>
-      </c>
-    </row>
-    <row r="31"/>
+        <v>162.5</v>
+      </c>
+    </row>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="29" t="n"/>
       <c r="B32" s="29" t="n"/>
@@ -1047,21 +1031,15 @@
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="17"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="A39" s="7" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1072,14 +1050,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,7 +880,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1049,15 +1049,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,7 +880,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,7 +880,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,7 +880,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1049,15 +1049,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,7 +880,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,10 +880,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45266</v>
+        <v>45258.54558033208</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -939,6 +943,17 @@
       <c r="F11" s="26" t="n"/>
       <c r="G11" s="26" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -994,7 +1009,7 @@
       </c>
       <c r="C29" s="43" t="n"/>
       <c r="D29" s="44" t="n">
-        <v>150</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1010,9 +1025,10 @@
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>162.5</v>
-      </c>
-    </row>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="29" t="n"/>
       <c r="B32" s="29" t="n"/>
@@ -1031,15 +1047,21 @@
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="17"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="A39" s="7" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="n"/>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1050,14 +1072,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
+++ b/LISTAS/mi/CINTA PERSIANA DISMAY.xlsx
@@ -880,14 +880,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="n">
-        <v>45258.54558033208</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -943,17 +939,6 @@
       <c r="F11" s="26" t="n"/>
       <c r="G11" s="26" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1009,7 +994,7 @@
       </c>
       <c r="C29" s="43" t="n"/>
       <c r="D29" s="44" t="n">
-        <v>222</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1025,10 +1010,9 @@
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="31"/>
+        <v>162.5</v>
+      </c>
+    </row>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="29" t="n"/>
       <c r="B32" s="29" t="n"/>
@@ -1047,21 +1031,15 @@
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="17"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39" ht="19.5" customHeight="1" s="17">
       <c r="A39" s="7" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="6" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -1071,15 +1049,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
